--- a/Docs/Bloque Asignaciones SDetalleVtas.xlsx
+++ b/Docs/Bloque Asignaciones SDetalleVtas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Desarrollos\MyPython\Tkinter\ArkConInv\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FE0EAE-57F6-4CA9-958E-996D02DD71C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCF5A7F1-9DC1-4757-B2BA-F3F7894FA70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1135,7 +1135,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1153,6 +1153,7 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1538,7 +1539,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>192</v>
@@ -1555,7 +1556,8 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2</v>
+        <f>A2+1</f>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>87</v>
@@ -1572,7 +1574,8 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>3</v>
+        <f t="shared" ref="A4:A67" si="0">A3+1</f>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>88</v>
@@ -1589,13 +1592,14 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>89</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>0</v>
@@ -1606,13 +1610,15 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>90</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <f>C5+1</f>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
@@ -1623,13 +1629,15 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>91</v>
       </c>
       <c r="C7" s="2">
-        <v>3</v>
+        <f t="shared" ref="C7:C70" si="1">C6+1</f>
+        <v>2</v>
       </c>
       <c r="D7" t="s">
         <v>2</v>
@@ -1640,13 +1648,15 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>7</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>92</v>
       </c>
       <c r="C8" s="2">
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
@@ -1657,13 +1667,15 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>93</v>
       </c>
       <c r="C9" s="2">
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>4</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
@@ -1674,13 +1686,15 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9</v>
+        <f t="shared" si="0"/>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>94</v>
       </c>
       <c r="C10" s="2">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -1691,13 +1705,15 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <f t="shared" si="0"/>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>95</v>
       </c>
       <c r="C11" s="2">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -1708,13 +1724,15 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>96</v>
       </c>
       <c r="C12" s="2">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
         <v>7</v>
@@ -1725,13 +1743,15 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>97</v>
       </c>
       <c r="C13" s="2">
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
@@ -1742,13 +1762,15 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
         <v>98</v>
       </c>
       <c r="C14" s="2">
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -1759,13 +1781,15 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>99</v>
       </c>
       <c r="C15" s="2">
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -1776,13 +1800,15 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>15</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>100</v>
       </c>
       <c r="C16" s="2">
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -1793,13 +1819,15 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>16</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
         <v>101</v>
       </c>
       <c r="C17" s="2">
-        <v>13</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
         <v>12</v>
@@ -1810,13 +1838,15 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>102</v>
       </c>
       <c r="C18" s="2">
-        <v>14</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
         <v>13</v>
@@ -1827,13 +1857,15 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
         <v>103</v>
       </c>
       <c r="C19" s="2">
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
         <v>14</v>
@@ -1844,13 +1876,15 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>19</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>104</v>
       </c>
       <c r="C20" s="2">
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
@@ -1861,13 +1895,15 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>20</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>105</v>
       </c>
       <c r="C21" s="2">
-        <v>17</v>
+        <f t="shared" si="1"/>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
@@ -1878,13 +1914,15 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>21</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>106</v>
       </c>
       <c r="C22" s="2">
-        <v>18</v>
+        <f t="shared" si="1"/>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -1895,13 +1933,15 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>22</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>107</v>
       </c>
       <c r="C23" s="2">
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>18</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -1912,13 +1952,15 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>23</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
         <v>108</v>
       </c>
       <c r="C24" s="2">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
       <c r="D24" t="s">
         <v>19</v>
@@ -1929,13 +1971,15 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
         <v>109</v>
       </c>
       <c r="C25" s="2">
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
         <v>20</v>
@@ -1946,13 +1990,15 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>110</v>
       </c>
       <c r="C26" s="2">
-        <v>22</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
@@ -1963,13 +2009,15 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="B27" t="s">
         <v>111</v>
       </c>
       <c r="C27" s="2">
-        <v>23</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
@@ -1980,13 +2028,15 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>27</v>
+        <f t="shared" si="0"/>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
         <v>112</v>
       </c>
       <c r="C28" s="2">
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="D28" t="s">
         <v>23</v>
@@ -1997,13 +2047,15 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>28</v>
+        <f t="shared" si="0"/>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
         <v>113</v>
       </c>
       <c r="C29" s="2">
-        <v>25</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
       <c r="D29" t="s">
         <v>24</v>
@@ -2014,13 +2066,15 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>29</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
         <v>114</v>
       </c>
       <c r="C30" s="2">
-        <v>26</v>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
         <v>25</v>
@@ -2031,13 +2085,15 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
         <v>115</v>
       </c>
       <c r="C31" s="2">
-        <v>27</v>
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
         <v>26</v>
@@ -2048,13 +2104,15 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>31</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="B32" t="s">
         <v>116</v>
       </c>
       <c r="C32" s="2">
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
         <v>27</v>
@@ -2065,13 +2123,15 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>32</v>
+        <f t="shared" si="0"/>
+        <v>31</v>
       </c>
       <c r="B33" t="s">
         <v>117</v>
       </c>
       <c r="C33" s="2">
-        <v>29</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
         <v>28</v>
@@ -2082,15 +2142,17 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>33</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
         <v>118</v>
       </c>
       <c r="C34" s="2">
-        <v>30</v>
-      </c>
-      <c r="D34" t="s">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F34" t="s">
@@ -2099,15 +2161,17 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>34</v>
+        <f t="shared" si="0"/>
+        <v>33</v>
       </c>
       <c r="B35" t="s">
         <v>119</v>
       </c>
       <c r="C35" s="2">
-        <v>31</v>
-      </c>
-      <c r="D35" t="s">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>30</v>
       </c>
       <c r="F35" t="s">
@@ -2116,13 +2180,15 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>35</v>
+        <f t="shared" si="0"/>
+        <v>34</v>
       </c>
       <c r="B36" t="s">
         <v>120</v>
       </c>
       <c r="C36" s="2">
-        <v>32</v>
+        <f t="shared" si="1"/>
+        <v>31</v>
       </c>
       <c r="D36" t="s">
         <v>31</v>
@@ -2133,13 +2199,15 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>36</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="B37" t="s">
         <v>121</v>
       </c>
       <c r="C37" s="2">
-        <v>33</v>
+        <f t="shared" si="1"/>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
         <v>32</v>
@@ -2150,13 +2218,15 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>37</v>
+        <f t="shared" si="0"/>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>122</v>
       </c>
       <c r="C38" s="2">
-        <v>34</v>
+        <f t="shared" si="1"/>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
         <v>33</v>
@@ -2167,13 +2237,15 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>38</v>
+        <f t="shared" si="0"/>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
         <v>123</v>
       </c>
       <c r="C39" s="2">
-        <v>35</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
       <c r="D39" t="s">
         <v>34</v>
@@ -2184,13 +2256,15 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>39</v>
+        <f t="shared" si="0"/>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
         <v>124</v>
       </c>
       <c r="C40" s="2">
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>35</v>
       </c>
       <c r="D40" t="s">
         <v>35</v>
@@ -2201,13 +2275,15 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>39</v>
       </c>
       <c r="B41" t="s">
         <v>125</v>
       </c>
       <c r="C41" s="2">
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>36</v>
       </c>
       <c r="D41" t="s">
         <v>36</v>
@@ -2218,13 +2294,15 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>41</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="B42" t="s">
         <v>126</v>
       </c>
       <c r="C42" s="2">
-        <v>38</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
       <c r="D42" t="s">
         <v>37</v>
@@ -2235,13 +2313,15 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
         <v>127</v>
       </c>
       <c r="C43" s="2">
-        <v>39</v>
+        <f t="shared" si="1"/>
+        <v>38</v>
       </c>
       <c r="D43" t="s">
         <v>38</v>
@@ -2252,13 +2332,15 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>43</v>
+        <f t="shared" si="0"/>
+        <v>42</v>
       </c>
       <c r="B44" t="s">
         <v>128</v>
       </c>
       <c r="C44" s="2">
-        <v>40</v>
+        <f t="shared" si="1"/>
+        <v>39</v>
       </c>
       <c r="D44" t="s">
         <v>39</v>
@@ -2269,13 +2351,15 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>44</v>
+        <f t="shared" si="0"/>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
         <v>129</v>
       </c>
       <c r="C45" s="2">
-        <v>41</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
       <c r="D45" t="s">
         <v>40</v>
@@ -2286,13 +2370,15 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>45</v>
+        <f t="shared" si="0"/>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
         <v>130</v>
       </c>
       <c r="C46" s="2">
-        <v>42</v>
+        <f t="shared" si="1"/>
+        <v>41</v>
       </c>
       <c r="D46" t="s">
         <v>41</v>
@@ -2303,13 +2389,15 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>46</v>
+        <f t="shared" si="0"/>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
         <v>131</v>
       </c>
       <c r="C47" s="2">
-        <v>43</v>
+        <f t="shared" si="1"/>
+        <v>42</v>
       </c>
       <c r="D47" t="s">
         <v>42</v>
@@ -2320,13 +2408,15 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>47</v>
+        <f t="shared" si="0"/>
+        <v>46</v>
       </c>
       <c r="B48" t="s">
         <v>132</v>
       </c>
       <c r="C48" s="2">
-        <v>44</v>
+        <f t="shared" si="1"/>
+        <v>43</v>
       </c>
       <c r="D48" t="s">
         <v>43</v>
@@ -2337,13 +2427,15 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>48</v>
+        <f t="shared" si="0"/>
+        <v>47</v>
       </c>
       <c r="B49" t="s">
         <v>133</v>
       </c>
       <c r="C49" s="2">
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
         <v>44</v>
@@ -2354,13 +2446,15 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>49</v>
+        <f t="shared" si="0"/>
+        <v>48</v>
       </c>
       <c r="B50" t="s">
         <v>134</v>
       </c>
       <c r="C50" s="2">
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>45</v>
       </c>
       <c r="D50" t="s">
         <v>45</v>
@@ -2371,13 +2465,15 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
         <v>135</v>
       </c>
       <c r="C51" s="2">
-        <v>47</v>
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
         <v>46</v>
@@ -2388,13 +2484,15 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>51</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="B52" t="s">
         <v>136</v>
       </c>
       <c r="C52" s="2">
-        <v>48</v>
+        <f t="shared" si="1"/>
+        <v>47</v>
       </c>
       <c r="D52" t="s">
         <v>47</v>
@@ -2405,13 +2503,15 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>52</v>
+        <f t="shared" si="0"/>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
         <v>137</v>
       </c>
       <c r="C53" s="2">
-        <v>49</v>
+        <f t="shared" si="1"/>
+        <v>48</v>
       </c>
       <c r="D53" t="s">
         <v>48</v>
@@ -2422,13 +2522,15 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>53</v>
+        <f t="shared" si="0"/>
+        <v>52</v>
       </c>
       <c r="B54" t="s">
         <v>138</v>
       </c>
       <c r="C54" s="2">
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>49</v>
       </c>
       <c r="D54" t="s">
         <v>49</v>
@@ -2439,13 +2541,15 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>54</v>
+        <f t="shared" si="0"/>
+        <v>53</v>
       </c>
       <c r="B55" t="s">
         <v>139</v>
       </c>
       <c r="C55" s="2">
-        <v>51</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
       <c r="D55" t="s">
         <v>50</v>
@@ -2456,13 +2560,15 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>55</v>
+        <f t="shared" si="0"/>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
         <v>140</v>
       </c>
       <c r="C56" s="2">
-        <v>52</v>
+        <f t="shared" si="1"/>
+        <v>51</v>
       </c>
       <c r="D56" t="s">
         <v>51</v>
@@ -2473,13 +2579,15 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>56</v>
+        <f t="shared" si="0"/>
+        <v>55</v>
       </c>
       <c r="B57" t="s">
         <v>141</v>
       </c>
       <c r="C57" s="2">
-        <v>53</v>
+        <f t="shared" si="1"/>
+        <v>52</v>
       </c>
       <c r="D57" t="s">
         <v>52</v>
@@ -2490,13 +2598,15 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>57</v>
+        <f t="shared" si="0"/>
+        <v>56</v>
       </c>
       <c r="B58" t="s">
         <v>142</v>
       </c>
       <c r="C58" s="2">
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>53</v>
       </c>
       <c r="D58" t="s">
         <v>53</v>
@@ -2507,13 +2617,15 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>58</v>
+        <f t="shared" si="0"/>
+        <v>57</v>
       </c>
       <c r="B59" t="s">
         <v>143</v>
       </c>
       <c r="C59" s="2">
-        <v>55</v>
+        <f t="shared" si="1"/>
+        <v>54</v>
       </c>
       <c r="D59" t="s">
         <v>54</v>
@@ -2524,13 +2636,15 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>59</v>
+        <f t="shared" si="0"/>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
         <v>144</v>
       </c>
       <c r="C60" s="2">
-        <v>56</v>
+        <f t="shared" si="1"/>
+        <v>55</v>
       </c>
       <c r="D60" t="s">
         <v>55</v>
@@ -2541,13 +2655,15 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
         <v>145</v>
       </c>
       <c r="C61" s="2">
-        <v>57</v>
+        <f t="shared" si="1"/>
+        <v>56</v>
       </c>
       <c r="D61" t="s">
         <v>56</v>
@@ -2558,13 +2674,15 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>61</v>
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
         <v>146</v>
       </c>
       <c r="C62" s="2">
-        <v>58</v>
+        <f t="shared" si="1"/>
+        <v>57</v>
       </c>
       <c r="D62" t="s">
         <v>57</v>
@@ -2575,13 +2693,15 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>62</v>
+        <f t="shared" si="0"/>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
         <v>147</v>
       </c>
       <c r="C63" s="2">
-        <v>59</v>
+        <f t="shared" si="1"/>
+        <v>58</v>
       </c>
       <c r="D63" t="s">
         <v>58</v>
@@ -2592,13 +2712,15 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>63</v>
+        <f t="shared" si="0"/>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
         <v>148</v>
       </c>
       <c r="C64" s="2">
-        <v>60</v>
+        <f t="shared" si="1"/>
+        <v>59</v>
       </c>
       <c r="D64" t="s">
         <v>59</v>
@@ -2609,13 +2731,15 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>64</v>
+        <f t="shared" si="0"/>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
         <v>149</v>
       </c>
       <c r="C65" s="2">
-        <v>61</v>
+        <f t="shared" si="1"/>
+        <v>60</v>
       </c>
       <c r="D65" t="s">
         <v>60</v>
@@ -2626,13 +2750,15 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>65</v>
+        <f t="shared" si="0"/>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
         <v>150</v>
       </c>
       <c r="C66" s="2">
-        <v>62</v>
+        <f t="shared" si="1"/>
+        <v>61</v>
       </c>
       <c r="D66" t="s">
         <v>61</v>
@@ -2643,13 +2769,15 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>66</v>
+        <f t="shared" si="0"/>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
         <v>151</v>
       </c>
       <c r="C67" s="2">
-        <v>63</v>
+        <f t="shared" si="1"/>
+        <v>62</v>
       </c>
       <c r="D67" t="s">
         <v>62</v>
@@ -2660,13 +2788,15 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>67</v>
+        <f t="shared" ref="A68:A98" si="2">A67+1</f>
+        <v>66</v>
       </c>
       <c r="B68" t="s">
         <v>152</v>
       </c>
       <c r="C68" s="2">
-        <v>64</v>
+        <f t="shared" si="1"/>
+        <v>63</v>
       </c>
       <c r="D68" t="s">
         <v>63</v>
@@ -2677,13 +2807,15 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>68</v>
+        <f t="shared" si="2"/>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
         <v>153</v>
       </c>
       <c r="C69" s="2">
-        <v>65</v>
+        <f t="shared" si="1"/>
+        <v>64</v>
       </c>
       <c r="D69" t="s">
         <v>64</v>
@@ -2694,13 +2826,15 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>69</v>
+        <f t="shared" si="2"/>
+        <v>68</v>
       </c>
       <c r="B70" t="s">
         <v>154</v>
       </c>
       <c r="C70" s="2">
-        <v>66</v>
+        <f t="shared" si="1"/>
+        <v>65</v>
       </c>
       <c r="D70" t="s">
         <v>65</v>
@@ -2711,13 +2845,15 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>70</v>
+        <f t="shared" si="2"/>
+        <v>69</v>
       </c>
       <c r="B71" t="s">
         <v>155</v>
       </c>
       <c r="C71" s="2">
-        <v>67</v>
+        <f t="shared" ref="C71:C90" si="3">C70+1</f>
+        <v>66</v>
       </c>
       <c r="D71" t="s">
         <v>66</v>
@@ -2728,13 +2864,15 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>71</v>
+        <f t="shared" si="2"/>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
         <v>156</v>
       </c>
       <c r="C72" s="2">
-        <v>68</v>
+        <f t="shared" si="3"/>
+        <v>67</v>
       </c>
       <c r="D72" t="s">
         <v>67</v>
@@ -2745,13 +2883,15 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>72</v>
+        <f t="shared" si="2"/>
+        <v>71</v>
       </c>
       <c r="B73" t="s">
         <v>157</v>
       </c>
       <c r="C73" s="2">
-        <v>69</v>
+        <f t="shared" si="3"/>
+        <v>68</v>
       </c>
       <c r="D73" t="s">
         <v>68</v>
@@ -2762,13 +2902,15 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>73</v>
+        <f t="shared" si="2"/>
+        <v>72</v>
       </c>
       <c r="B74" t="s">
         <v>158</v>
       </c>
       <c r="C74" s="2">
-        <v>70</v>
+        <f t="shared" si="3"/>
+        <v>69</v>
       </c>
       <c r="D74" t="s">
         <v>69</v>
@@ -2779,13 +2921,15 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>74</v>
+        <f t="shared" si="2"/>
+        <v>73</v>
       </c>
       <c r="B75" t="s">
         <v>188</v>
       </c>
       <c r="C75" s="2">
-        <v>71</v>
+        <f t="shared" si="3"/>
+        <v>70</v>
       </c>
       <c r="D75" t="s">
         <v>70</v>
@@ -2796,13 +2940,15 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>75</v>
+        <f t="shared" si="2"/>
+        <v>74</v>
       </c>
       <c r="B76" t="s">
         <v>159</v>
       </c>
       <c r="C76" s="2">
-        <v>72</v>
+        <f t="shared" si="3"/>
+        <v>71</v>
       </c>
       <c r="D76" t="s">
         <v>71</v>
@@ -2813,13 +2959,15 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>76</v>
+        <f t="shared" si="2"/>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
         <v>160</v>
       </c>
       <c r="C77" s="2">
-        <v>73</v>
+        <f t="shared" si="3"/>
+        <v>72</v>
       </c>
       <c r="D77" t="s">
         <v>72</v>
@@ -2830,13 +2978,15 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>77</v>
+        <f t="shared" si="2"/>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
         <v>161</v>
       </c>
       <c r="C78" s="2">
-        <v>74</v>
+        <f t="shared" si="3"/>
+        <v>73</v>
       </c>
       <c r="D78" t="s">
         <v>73</v>
@@ -2847,13 +2997,15 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>78</v>
+        <f t="shared" si="2"/>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
         <v>162</v>
       </c>
       <c r="C79" s="2">
-        <v>75</v>
+        <f t="shared" si="3"/>
+        <v>74</v>
       </c>
       <c r="D79" t="s">
         <v>74</v>
@@ -2864,13 +3016,15 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>79</v>
+        <f t="shared" si="2"/>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
         <v>163</v>
       </c>
       <c r="C80" s="2">
-        <v>76</v>
+        <f t="shared" si="3"/>
+        <v>75</v>
       </c>
       <c r="D80" t="s">
         <v>75</v>
@@ -2881,13 +3035,15 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>80</v>
+        <f t="shared" si="2"/>
+        <v>79</v>
       </c>
       <c r="B81" t="s">
         <v>164</v>
       </c>
       <c r="C81" s="2">
-        <v>77</v>
+        <f t="shared" si="3"/>
+        <v>76</v>
       </c>
       <c r="D81" t="s">
         <v>76</v>
@@ -2898,13 +3054,15 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>81</v>
+        <f t="shared" si="2"/>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
         <v>165</v>
       </c>
       <c r="C82" s="2">
-        <v>78</v>
+        <f t="shared" si="3"/>
+        <v>77</v>
       </c>
       <c r="D82" t="s">
         <v>77</v>
@@ -2915,13 +3073,15 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>82</v>
+        <f t="shared" si="2"/>
+        <v>81</v>
       </c>
       <c r="B83" t="s">
         <v>166</v>
       </c>
       <c r="C83" s="2">
-        <v>79</v>
+        <f t="shared" si="3"/>
+        <v>78</v>
       </c>
       <c r="D83" t="s">
         <v>78</v>
@@ -2932,13 +3092,15 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>83</v>
+        <f t="shared" si="2"/>
+        <v>82</v>
       </c>
       <c r="B84" t="s">
         <v>167</v>
       </c>
       <c r="C84" s="2">
-        <v>80</v>
+        <f t="shared" si="3"/>
+        <v>79</v>
       </c>
       <c r="D84" t="s">
         <v>79</v>
@@ -2949,13 +3111,15 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>84</v>
+        <f t="shared" si="2"/>
+        <v>83</v>
       </c>
       <c r="B85" t="s">
         <v>168</v>
       </c>
       <c r="C85" s="2">
-        <v>81</v>
+        <f t="shared" si="3"/>
+        <v>80</v>
       </c>
       <c r="D85" t="s">
         <v>80</v>
@@ -2966,13 +3130,15 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>85</v>
+        <f t="shared" si="2"/>
+        <v>84</v>
       </c>
       <c r="B86" t="s">
         <v>169</v>
       </c>
       <c r="C86" s="2">
-        <v>82</v>
+        <f t="shared" si="3"/>
+        <v>81</v>
       </c>
       <c r="D86" t="s">
         <v>81</v>
@@ -2983,13 +3149,15 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>86</v>
+        <f t="shared" si="2"/>
+        <v>85</v>
       </c>
       <c r="B87" t="s">
         <v>170</v>
       </c>
       <c r="C87" s="2">
-        <v>83</v>
+        <f t="shared" si="3"/>
+        <v>82</v>
       </c>
       <c r="D87" t="s">
         <v>82</v>
@@ -3000,13 +3168,15 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>87</v>
+        <f t="shared" si="2"/>
+        <v>86</v>
       </c>
       <c r="B88" t="s">
         <v>171</v>
       </c>
       <c r="C88" s="2">
-        <v>84</v>
+        <f t="shared" si="3"/>
+        <v>83</v>
       </c>
       <c r="D88" t="s">
         <v>83</v>
@@ -3017,13 +3187,15 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>88</v>
+        <f t="shared" si="2"/>
+        <v>87</v>
       </c>
       <c r="B89" t="s">
         <v>172</v>
       </c>
       <c r="C89" s="2">
-        <v>85</v>
+        <f t="shared" si="3"/>
+        <v>84</v>
       </c>
       <c r="D89" t="s">
         <v>84</v>
@@ -3034,13 +3206,15 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>89</v>
+        <f t="shared" si="2"/>
+        <v>88</v>
       </c>
       <c r="B90" t="s">
         <v>173</v>
       </c>
       <c r="C90" s="2">
-        <v>86</v>
+        <f t="shared" si="3"/>
+        <v>85</v>
       </c>
       <c r="D90" t="s">
         <v>85</v>
@@ -3051,7 +3225,8 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>90</v>
+        <f t="shared" si="2"/>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
         <v>174</v>
@@ -3068,7 +3243,8 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>91</v>
+        <f t="shared" si="2"/>
+        <v>90</v>
       </c>
       <c r="B92" t="s">
         <v>175</v>
@@ -3085,7 +3261,8 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>92</v>
+        <f t="shared" si="2"/>
+        <v>91</v>
       </c>
       <c r="B93" t="s">
         <v>176</v>
@@ -3102,7 +3279,8 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
-        <v>93</v>
+        <f t="shared" si="2"/>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
         <v>177</v>
@@ -3119,7 +3297,8 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
-        <v>94</v>
+        <f t="shared" si="2"/>
+        <v>93</v>
       </c>
       <c r="B95" t="s">
         <v>178</v>
@@ -3136,7 +3315,8 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
-        <v>95</v>
+        <f t="shared" si="2"/>
+        <v>94</v>
       </c>
       <c r="B96" t="s">
         <v>179</v>
@@ -3153,7 +3333,8 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
-        <v>96</v>
+        <f t="shared" si="2"/>
+        <v>95</v>
       </c>
       <c r="B97" t="s">
         <v>180</v>
@@ -3170,7 +3351,8 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
-        <v>97</v>
+        <f t="shared" si="2"/>
+        <v>96</v>
       </c>
       <c r="B98" t="s">
         <v>181</v>
